--- a/Exp3_PTO_GRPO/eda/results/L5/tables/6_stats/6_stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L5/tables/6_stats/6_stats.xlsx
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.675</v>
+        <v>2.839</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.547</v>
+        <v>0.523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.494</v>
+        <v>0.483</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.328</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.766</v>
+        <v>0.729</v>
       </c>
       <c r="L5" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.675</v>
+        <v>2.839</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.547</v>
+        <v>0.523</v>
       </c>
       <c r="G14" t="n">
-        <v>0.494</v>
+        <v>0.483</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.328</v>
+        <v>0.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.766</v>
+        <v>0.729</v>
       </c>
       <c r="L14" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.167</v>
+        <v>41.5716</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0968</v>
+        <v>0.1083</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -2050,10 +2050,10 @@
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0174</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.017</v>
+        <v>-0.0091</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1412</v>
+        <v>0.1416</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="3">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
     </row>
   </sheetData>
